--- a/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-bundle.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-bundle.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.0</t>
+    <t>1.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-16T08:31:54+00:00</t>
+    <t>2026-02-16T11:13:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-bundle.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-bundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-16T11:13:42+00:00</t>
+    <t>2026-02-17T09:00:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-bundle.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-bundle.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0</t>
+    <t>1.1.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-17T09:00:43+00:00</t>
+    <t>2026-09-01T07:40:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
